--- a/construction_cost_predictor/outputs/03_feature_stats.xlsx
+++ b/construction_cost_predictor/outputs/03_feature_stats.xlsx
@@ -441,7 +441,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>366.6536712410918</v>
+        <v>383.9797841379867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>272.3840697538912</v>
+        <v>307.5361309507697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>129.576819800827</v>
+        <v>175.6882252264271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.9013771658318</v>
+        <v>92.09937207595659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.85986133394479</v>
+        <v>16.63715103619324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -516,11 +516,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.118036049906452</v>
+        <v>10.51682571495908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>△ 中等</t>
+          <t>⚠ 严重</t>
         </is>
       </c>
     </row>
@@ -531,11 +531,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.526559896789407</v>
+        <v>5.333306218675353</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>✓ 正常</t>
+          <t>△ 中等</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.662061014271884</v>
+        <v>2.664151162447066</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.341237948994233</v>
+        <v>2.513537698332851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.218419933691026</v>
+        <v>1.313875678632305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -665,34 +665,34 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09246593268978374</v>
+        <v>0.006210091433610591</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06280745959485932</v>
+        <v>0.0348506879272432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02390380781405235</v>
+        <v>0.03016201078487042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0501355451653791</v>
+        <v>-0.01895738142917426</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01843290305859818</v>
+        <v>-0.02387723356925938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4705340478976702</v>
+        <v>0.4390429517653321</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01287194114950792</v>
+        <v>0.008711890667776036</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.01849987693059934</v>
+        <v>-0.01985746024301003</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1188453657521307</v>
+        <v>-0.00583680438000638</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01321854882180049</v>
+        <v>-0.02703162231171881</v>
       </c>
     </row>
     <row r="3">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09246593268978374</v>
+        <v>0.006210091433610591</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02095089003695866</v>
+        <v>0.0273443181341768</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08288656236510861</v>
+        <v>0.0469099310041779</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0008324338138083219</v>
+        <v>-0.0551249026298849</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001419677385330994</v>
+        <v>-0.05000703961524049</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6580351161649353</v>
+        <v>-0.6534195364100807</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02053462161992602</v>
+        <v>-0.04252486989506651</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03377146749289795</v>
+        <v>0.07808498297980228</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8028787779568266</v>
+        <v>0.7692081330374414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08809308477133959</v>
+        <v>0.1583059617686915</v>
       </c>
     </row>
     <row r="4">
@@ -742,37 +742,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06280745959485932</v>
+        <v>0.0348506879272432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02095089003695866</v>
+        <v>0.0273443181341768</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002002888635545491</v>
+        <v>-0.06046613523907548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01142377782917967</v>
+        <v>0.01619856674201171</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.02671523390488563</v>
+        <v>-0.002399716114475691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03857660581149765</v>
+        <v>-0.01338428305501381</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08864238990294172</v>
+        <v>-0.02019480903309154</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.02394923652331347</v>
+        <v>0.06639244753117161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03308482008581907</v>
+        <v>0.01142653871688741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02645708363884752</v>
+        <v>0.01734879880076731</v>
       </c>
     </row>
     <row r="5">
@@ -782,37 +782,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.02390380781405235</v>
+        <v>0.03016201078487042</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08288656236510861</v>
+        <v>0.0469099310041779</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002002888635545491</v>
+        <v>-0.06046613523907548</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.09915424686631047</v>
+        <v>-0.05365817295212149</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0734770459874013</v>
+        <v>-0.010690504696034</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0208913296327475</v>
+        <v>-0.05058661747454775</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02199078143808322</v>
+        <v>0.08698294553954952</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.007337542775131584</v>
+        <v>0.1592893478824778</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03451727720658121</v>
+        <v>0.01711500334023497</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02223419124730523</v>
+        <v>0.05496672692443481</v>
       </c>
     </row>
     <row r="6">
@@ -822,37 +822,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0501355451653791</v>
+        <v>-0.01895738142917426</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0008324338138083219</v>
+        <v>-0.0551249026298849</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01142377782917967</v>
+        <v>0.01619856674201171</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.09915424686631047</v>
+        <v>-0.05365817295212149</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9126123840447737</v>
+        <v>0.9218837814635791</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001717546693012548</v>
+        <v>0.002023609582278614</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02157349059170056</v>
+        <v>0.07585888393439834</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0308302172168863</v>
+        <v>0.03527280595944208</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005754484842640137</v>
+        <v>-0.0455846513879402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4541900209161892</v>
+        <v>0.5314780497017103</v>
       </c>
     </row>
     <row r="7">
@@ -862,37 +862,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01843290305859818</v>
+        <v>-0.02387723356925938</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001419677385330994</v>
+        <v>-0.05000703961524049</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02671523390488563</v>
+        <v>-0.002399716114475691</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0734770459874013</v>
+        <v>-0.010690504696034</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9126123840447737</v>
+        <v>0.9218837814635791</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01391786716029393</v>
+        <v>0.007843271344629433</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02302885313118191</v>
+        <v>0.03738716429943198</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03385834291658501</v>
+        <v>0.03716469214201511</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.007426157716665326</v>
+        <v>-0.03713524214645866</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4183282862230884</v>
+        <v>0.472539466697201</v>
       </c>
     </row>
     <row r="8">
@@ -902,37 +902,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4705340478976702</v>
+        <v>0.4390429517653321</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6580351161649353</v>
+        <v>-0.6534195364100807</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03857660581149765</v>
+        <v>-0.01338428305501381</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0208913296327475</v>
+        <v>-0.05058661747454775</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.001717546693012548</v>
+        <v>0.002023609582278614</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01391786716029393</v>
+        <v>0.007843271344629433</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05814392023141425</v>
+        <v>-0.01565056668929898</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01738990068531414</v>
+        <v>-0.06041268494199843</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6403804419239799</v>
+        <v>-0.6277878059791213</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.02622326398625318</v>
+        <v>-0.1161796360337707</v>
       </c>
     </row>
     <row r="9">
@@ -942,37 +942,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.01287194114950792</v>
+        <v>0.008711890667776036</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.02053462161992602</v>
+        <v>-0.04252486989506651</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08864238990294172</v>
+        <v>-0.02019480903309154</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02199078143808322</v>
+        <v>0.08698294553954952</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02157349059170056</v>
+        <v>0.07585888393439834</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.02302885313118191</v>
+        <v>0.03738716429943198</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05814392023141425</v>
+        <v>-0.01565056668929898</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04871060083949919</v>
+        <v>0.07022592534175502</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03349955764709334</v>
+        <v>-0.01188950304981054</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3142155727816441</v>
+        <v>0.3349230770192234</v>
       </c>
     </row>
     <row r="10">
@@ -982,37 +982,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.01849987693059934</v>
+        <v>-0.01985746024301003</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03377146749289795</v>
+        <v>0.07808498297980228</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02394923652331347</v>
+        <v>0.06639244753117161</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.007337542775131584</v>
+        <v>0.1592893478824778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0308302172168863</v>
+        <v>0.03527280595944208</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03385834291658501</v>
+        <v>0.03716469214201511</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01738990068531414</v>
+        <v>-0.06041268494199843</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04871060083949919</v>
+        <v>0.07022592534175502</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009992886240929774</v>
+        <v>0.03282833201373712</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02847403877448432</v>
+        <v>0.1101828685132255</v>
       </c>
     </row>
     <row r="11">
@@ -1022,37 +1022,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1188453657521307</v>
+        <v>-0.00583680438000638</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8028787779568266</v>
+        <v>0.7692081330374414</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03308482008581907</v>
+        <v>0.01142653871688741</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03451727720658121</v>
+        <v>0.01711500334023497</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.005754484842640137</v>
+        <v>-0.0455846513879402</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.007426157716665326</v>
+        <v>-0.03713524214645866</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6403804419239799</v>
+        <v>-0.6277878059791213</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.03349955764709334</v>
+        <v>-0.01188950304981054</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009992886240929774</v>
+        <v>0.03282833201373712</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06798470578244688</v>
+        <v>0.07465859347487033</v>
       </c>
     </row>
     <row r="12">
@@ -1062,34 +1062,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.01321854882180049</v>
+        <v>-0.02703162231171881</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08809308477133959</v>
+        <v>0.1583059617686915</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02645708363884752</v>
+        <v>0.01734879880076731</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02223419124730523</v>
+        <v>0.05496672692443481</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4541900209161892</v>
+        <v>0.5314780497017103</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4183282862230884</v>
+        <v>0.472539466697201</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.02622326398625318</v>
+        <v>-0.1161796360337707</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3142155727816441</v>
+        <v>0.3349230770192234</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02847403877448432</v>
+        <v>0.1101828685132255</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06798470578244688</v>
+        <v>0.07465859347487033</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
